--- a/ingest/uqn-fix-2026-09-25/review/مراجعة_التعديلات_والإحلالات_مع_السريان_المعاد.xlsx
+++ b/ingest/uqn-fix-2026-09-25/review/مراجعة_التعديلات_والإحلالات_مع_السريان_المعاد.xlsx
@@ -84,7 +84,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -108,6 +108,11 @@
         <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -128,7 +133,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -173,6 +178,9 @@
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -700,67 +708,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.85" customHeight="1" s="7">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>القرار</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>المراجع</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>ملاحظة / التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>المعرّف</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>النظام المستهدف</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>رمز حكيم</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>العملية</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>المادة</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>الفقرة</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>النص الجديد / العبارة الجديدة</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>العبارة القديمة</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>يسري من (هـ)</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>قاعدة السريان</t>
         </is>
@@ -775,27 +783,27 @@
           <t>سند السريان</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>المخاطر</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>الأداة</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>رقمها</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>رابط المصدر</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>نص البند من الأداة</t>
         </is>
@@ -15195,67 +15203,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.85" customHeight="1" s="7">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>القرار</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>المراجع</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>ملاحظة / التصحيح</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>المعرّف</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>النظام المستهدف</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>رمز حكيم</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>العملية</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>المادة</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>الفقرة</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>النص الجديد / العبارة الجديدة</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>العبارة القديمة</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>يسري من (هـ)</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>قاعدة السريان</t>
         </is>
@@ -15270,27 +15278,27 @@
           <t>سند السريان</t>
         </is>
       </c>
-      <c r="P1" s="11" t="inlineStr">
+      <c r="P1" s="12" t="inlineStr">
         <is>
           <t>المخاطر</t>
         </is>
       </c>
-      <c r="Q1" s="11" t="inlineStr">
+      <c r="Q1" s="12" t="inlineStr">
         <is>
           <t>الأداة</t>
         </is>
       </c>
-      <c r="R1" s="11" t="inlineStr">
+      <c r="R1" s="12" t="inlineStr">
         <is>
           <t>رقمها</t>
         </is>
       </c>
-      <c r="S1" s="11" t="inlineStr">
+      <c r="S1" s="12" t="inlineStr">
         <is>
           <t>رابط المصدر</t>
         </is>
       </c>
-      <c r="T1" s="11" t="inlineStr">
+      <c r="T1" s="12" t="inlineStr">
         <is>
           <t>نص البند من الأداة</t>
         </is>
@@ -18441,14 +18449,14 @@
           <t>من تاريخ النشر (افتراض — لم يُنص على مهلة في الأداة)</t>
         </is>
       </c>
-      <c r="N41" s="15" t="inlineStr">
-        <is>
-          <t>تعذّر</t>
-        </is>
-      </c>
-      <c r="O41" s="15" t="inlineStr">
-        <is>
-          <t>إحلال: تاريخ السريان في المادة الختامية للتنظيم/النظام الجديد، ونصه «بالصيغة المرافقة» لم يُنشر في صفحة الأداة ولم يُقرأ</t>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>1447-01-23</t>
+        </is>
+      </c>
+      <c r="O41" s="16" t="inlineStr">
+        <is>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-026 (قرار مجلس الوزراء 43، نافذ من 2025-07-18 = النشر 1447-01-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
         </is>
       </c>
       <c r="P41" s="9" t="inlineStr">
@@ -19866,14 +19874,14 @@
           <t>من تاريخ النشر (افتراض — لم يُنص على مهلة في الأداة)</t>
         </is>
       </c>
-      <c r="N59" s="15" t="inlineStr">
-        <is>
-          <t>تعذّر</t>
-        </is>
-      </c>
-      <c r="O59" s="15" t="inlineStr">
-        <is>
-          <t>إحلال: تاريخ السريان في المادة الختامية للتنظيم/النظام الجديد، ونصه «بالصيغة المرافقة» لم يُنشر في صفحة الأداة ولم يُقرأ</t>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>1446-11-25</t>
+        </is>
+      </c>
+      <c r="O59" s="16" t="inlineStr">
+        <is>
+          <t>التنظيم الجديد طُبّق في حكيم بمهمة HKM-028 (build_hkm028_new_editions.ts): المادة الخامسة عشرة «ويعمل به من تاريخ نشره» = 1446-11-25 (2025-05-23)، والقديم «مستبدل» — لا يُعتمد من الطابور تفاديًا لسجل مكرر</t>
         </is>
       </c>
       <c r="P59" s="9" t="inlineStr">
@@ -32768,57 +32776,57 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="7">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>المراجع</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>ملاحظة</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>رقم الأثر</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>النوع</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>الأداة</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>رقمها</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>تاريخها</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>النظام كما ورد</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>البنود غير المستخرجة</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>رابط المصدر</t>
         </is>
@@ -41720,67 +41728,67 @@
   </cols>
   <sheetData>
     <row r="1" ht="23.85" customHeight="1" s="7">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>الحالة</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>النظام القديم</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>رمز حكيم</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>سند القديم</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>النظام الجديد</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>العلاقة</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>يسري من (هـ)</t>
         </is>
       </c>
-      <c r="H1" s="11" t="inlineStr">
+      <c r="H1" s="12" t="inlineStr">
         <is>
           <t>قاعدة السريان</t>
         </is>
       </c>
-      <c r="I1" s="11" t="inlineStr">
+      <c r="I1" s="12" t="inlineStr">
         <is>
           <t>ساري الآن؟</t>
         </is>
       </c>
-      <c r="J1" s="11" t="inlineStr">
+      <c r="J1" s="12" t="inlineStr">
         <is>
           <t>نص الدليل</t>
         </is>
       </c>
-      <c r="K1" s="11" t="inlineStr">
+      <c r="K1" s="12" t="inlineStr">
         <is>
           <t>موضعه</t>
         </is>
       </c>
-      <c r="L1" s="11" t="inlineStr">
+      <c r="L1" s="12" t="inlineStr">
         <is>
           <t>رابط الدليل</t>
         </is>
       </c>
-      <c r="M1" s="11" t="inlineStr">
+      <c r="M1" s="12" t="inlineStr">
         <is>
           <t>ملاحظة</t>
         </is>
@@ -42876,37 +42884,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="7">
-      <c r="A1" s="11" t="inlineStr">
+      <c r="A1" s="12" t="inlineStr">
         <is>
           <t>العمل</t>
         </is>
       </c>
-      <c r="B1" s="11" t="inlineStr">
+      <c r="B1" s="12" t="inlineStr">
         <is>
           <t>نوع الأداة</t>
         </is>
       </c>
-      <c r="C1" s="11" t="inlineStr">
+      <c r="C1" s="12" t="inlineStr">
         <is>
           <t>رقمها</t>
         </is>
       </c>
-      <c r="D1" s="11" t="inlineStr">
+      <c r="D1" s="12" t="inlineStr">
         <is>
           <t>تاريخها (هـ)</t>
         </is>
       </c>
-      <c r="E1" s="11" t="inlineStr">
+      <c r="E1" s="12" t="inlineStr">
         <is>
           <t>عنوان الصفحة</t>
         </is>
       </c>
-      <c r="F1" s="11" t="inlineStr">
+      <c r="F1" s="12" t="inlineStr">
         <is>
           <t>البند المعتمِد</t>
         </is>
       </c>
-      <c r="G1" s="11" t="inlineStr">
+      <c r="G1" s="12" t="inlineStr">
         <is>
           <t>الرابط</t>
         </is>
